--- a/Nordic embedding data API pricin estimates.xlsx
+++ b/Nordic embedding data API pricin estimates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kgal/sw/embedding_dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D13E23B8-161B-F84C-A0B6-711D050601D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BA022F5-2FEE-EB4B-A5CD-F39FE8A8298F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="680" yWindow="660" windowWidth="28040" windowHeight="16980" xr2:uid="{4CAED55A-6CC8-0942-9C99-39986C26251A}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -77,7 +77,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="170" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -120,7 +120,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -496,7 +496,7 @@
       </c>
       <c r="E2" s="2">
         <f>Sheet1!B2*Sheet2!$A$2+(Sheet2!$B$2*Sheet1!C2)</f>
-        <v>175551000</v>
+        <v>175.55099999999999</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -514,7 +514,7 @@
       </c>
       <c r="E3" s="2">
         <f>Sheet1!B3*Sheet2!$A$2+(Sheet2!$B$2*Sheet1!C3)</f>
-        <v>88534000</v>
+        <v>88.533999999999992</v>
       </c>
     </row>
   </sheetData>
@@ -540,12 +540,12 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2">
-        <f>1000000*250</f>
-        <v>250000000</v>
+        <f>1000000*250/1000000</f>
+        <v>250</v>
       </c>
       <c r="B2">
-        <f>1000000*((38+200+23+500+30)/5)</f>
-        <v>158200000</v>
+        <f>1000000*((38+200+23+500+30)/5)/1000000</f>
+        <v>158.19999999999999</v>
       </c>
     </row>
   </sheetData>
